--- a/Project/Teams.xlsx
+++ b/Project/Teams.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch_29Oct25\all\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch_29Oct25\all\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A56F6535-FEB0-433A-A81B-85D91D00CA8A}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF82FFB1-4612-4760-89D2-02948205DC37}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{3D2F2C73-225E-4479-9257-01007F8BBF14}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t>Kanderi Reshma Sri</t>
   </si>
@@ -141,13 +141,58 @@
     <t>Team #</t>
   </si>
   <si>
-    <t>Project title</t>
-  </si>
-  <si>
     <t>Medicare Appointment System</t>
   </si>
   <si>
     <t>Healthcare Insurance Claim System</t>
+  </si>
+  <si>
+    <t>Realtime Online Bidding System</t>
+  </si>
+  <si>
+    <t>Medical Devices Inventory System</t>
+  </si>
+  <si>
+    <t>Fitness Tracker</t>
+  </si>
+  <si>
+    <t>Hospital Resource Managament</t>
+  </si>
+  <si>
+    <t>Mental Health Support &amp; Referral System</t>
+  </si>
+  <si>
+    <t>Clinic Management System</t>
+  </si>
+  <si>
+    <t>Team Name</t>
+  </si>
+  <si>
+    <t>Project Title</t>
+  </si>
+  <si>
+    <t>Care CodeX</t>
+  </si>
+  <si>
+    <t>The CODE-fathers</t>
+  </si>
+  <si>
+    <t>Tech Titans</t>
+  </si>
+  <si>
+    <t>MAD-Max</t>
+  </si>
+  <si>
+    <t>iQube</t>
+  </si>
+  <si>
+    <t>Code Behind Crew</t>
+  </si>
+  <si>
+    <t>Commit And Conquer</t>
+  </si>
+  <si>
+    <t>Nexus</t>
   </si>
 </sst>
 </file>
@@ -243,7 +288,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -256,23 +301,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="45" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="45" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="45" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="45" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -588,456 +624,530 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B63DBF80-82F6-4A1E-80CA-7E30825405E4}">
-  <dimension ref="B2:E36"/>
+  <dimension ref="B2:F36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="25.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1">
+        <v>302802</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B3" s="1" t="s">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B4" s="4"/>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1">
+        <v>302937</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B5" s="4"/>
+      <c r="C5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="1">
+        <v>302786</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B6" s="5"/>
+      <c r="C6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="1">
+        <v>302881</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="5"/>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="1">
+        <v>302794</v>
+      </c>
+      <c r="E7" s="1">
+        <v>2</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B8" s="4"/>
+      <c r="C8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="1">
+        <v>302801</v>
+      </c>
+      <c r="E8" s="1">
+        <v>2</v>
+      </c>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B9" s="4"/>
+      <c r="C9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="1">
+        <v>302791</v>
+      </c>
+      <c r="E9" s="1">
+        <v>2</v>
+      </c>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B10" s="4"/>
+      <c r="C10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="1">
+        <v>302796</v>
+      </c>
+      <c r="E10" s="1">
+        <v>2</v>
+      </c>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B11" s="5"/>
+      <c r="C11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="1">
+        <v>302970</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2</v>
+      </c>
+      <c r="F11" s="5"/>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B12" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="1">
+        <v>302800</v>
+      </c>
+      <c r="E12" s="1">
         <v>3</v>
       </c>
-      <c r="C3" s="1">
-        <v>302802</v>
-      </c>
-      <c r="D3" s="1">
+      <c r="F12" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B13" s="7"/>
+      <c r="C13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="1">
+        <v>302788</v>
+      </c>
+      <c r="E13" s="1">
+        <v>3</v>
+      </c>
+      <c r="F13" s="7"/>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B14" s="7"/>
+      <c r="C14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="1">
+        <v>302792</v>
+      </c>
+      <c r="E14" s="1">
+        <v>3</v>
+      </c>
+      <c r="F14" s="7"/>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B15" s="7"/>
+      <c r="C15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="1">
+        <v>302797</v>
+      </c>
+      <c r="E15" s="1">
+        <v>3</v>
+      </c>
+      <c r="F15" s="7"/>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B16" s="8"/>
+      <c r="C16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="1">
+        <v>302822</v>
+      </c>
+      <c r="E16" s="1">
+        <v>3</v>
+      </c>
+      <c r="F16" s="8"/>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B17" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="1">
+        <v>302785</v>
+      </c>
+      <c r="E17" s="1">
+        <v>4</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B18" s="4"/>
+      <c r="C18" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="1">
+        <v>302808</v>
+      </c>
+      <c r="E18" s="1">
+        <v>4</v>
+      </c>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B19" s="4"/>
+      <c r="C19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="1">
+        <v>302938</v>
+      </c>
+      <c r="E19" s="1">
+        <v>4</v>
+      </c>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B20" s="5"/>
+      <c r="C20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" s="1">
+        <v>302776</v>
+      </c>
+      <c r="E20" s="1">
+        <v>4</v>
+      </c>
+      <c r="F20" s="5"/>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B21" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="1">
+        <v>302783</v>
+      </c>
+      <c r="E21" s="1">
+        <v>5</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B22" s="4"/>
+      <c r="C22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="1">
+        <v>302905</v>
+      </c>
+      <c r="E22" s="1">
+        <v>5</v>
+      </c>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B23" s="4"/>
+      <c r="C23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="1">
+        <v>303032</v>
+      </c>
+      <c r="E23" s="1">
+        <v>5</v>
+      </c>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B24" s="5"/>
+      <c r="C24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="1">
+        <v>302817</v>
+      </c>
+      <c r="E24" s="1">
+        <v>5</v>
+      </c>
+      <c r="F24" s="5"/>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B25" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B4" s="1" t="s">
+      <c r="D25" s="1">
+        <v>302929</v>
+      </c>
+      <c r="E25" s="1">
+        <v>6</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B26" s="4"/>
+      <c r="C26" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="1">
+        <v>302787</v>
+      </c>
+      <c r="E26" s="1">
+        <v>6</v>
+      </c>
+      <c r="F26" s="4"/>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B27" s="4"/>
+      <c r="C27" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="1">
+        <v>302799</v>
+      </c>
+      <c r="E27" s="1">
+        <v>6</v>
+      </c>
+      <c r="F27" s="4"/>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B28" s="5"/>
+      <c r="C28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="1">
+        <v>302798</v>
+      </c>
+      <c r="E28" s="1">
+        <v>6</v>
+      </c>
+      <c r="F28" s="5"/>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B29" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D29" s="1">
+        <v>302784</v>
+      </c>
+      <c r="E29" s="1">
+        <v>7</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B30" s="4"/>
+      <c r="C30" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" s="1">
+        <v>302795</v>
+      </c>
+      <c r="E30" s="1">
+        <v>7</v>
+      </c>
+      <c r="F30" s="4"/>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B31" s="4"/>
+      <c r="C31" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31" s="1">
+        <v>302805</v>
+      </c>
+      <c r="E31" s="1">
+        <v>7</v>
+      </c>
+      <c r="F31" s="4"/>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B32" s="5"/>
+      <c r="C32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="1">
+        <v>302806</v>
+      </c>
+      <c r="E32" s="1">
+        <v>7</v>
+      </c>
+      <c r="F32" s="5"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B33" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D33" s="1">
+        <v>302814</v>
+      </c>
+      <c r="E33" s="1">
         <v>8</v>
       </c>
-      <c r="C4" s="1">
-        <v>302937</v>
-      </c>
-      <c r="D4" s="1">
-        <v>1</v>
-      </c>
-      <c r="E4" s="4"/>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="1">
-        <v>302786</v>
-      </c>
-      <c r="D5" s="1">
-        <v>1</v>
-      </c>
-      <c r="E5" s="4"/>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="1">
-        <v>302881</v>
-      </c>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" s="5"/>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="1">
-        <v>302794</v>
-      </c>
-      <c r="D7" s="1">
-        <v>2</v>
-      </c>
-      <c r="E7" s="9"/>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="1">
-        <v>302801</v>
-      </c>
-      <c r="D8" s="1">
-        <v>2</v>
-      </c>
-      <c r="E8" s="10"/>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="1">
-        <v>302791</v>
-      </c>
-      <c r="D9" s="1">
-        <v>2</v>
-      </c>
-      <c r="E9" s="10"/>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="1">
-        <v>302796</v>
-      </c>
-      <c r="D10" s="1">
-        <v>2</v>
-      </c>
-      <c r="E10" s="10"/>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="1">
-        <v>302970</v>
-      </c>
-      <c r="D11" s="1">
-        <v>2</v>
-      </c>
-      <c r="E11" s="11"/>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="1">
-        <v>302800</v>
-      </c>
-      <c r="D12" s="1">
-        <v>3</v>
-      </c>
-      <c r="E12" s="6"/>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="1">
-        <v>302788</v>
-      </c>
-      <c r="D13" s="1">
-        <v>3</v>
-      </c>
-      <c r="E13" s="7"/>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="1">
-        <v>302792</v>
-      </c>
-      <c r="D14" s="1">
-        <v>3</v>
-      </c>
-      <c r="E14" s="7"/>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" s="1">
-        <v>302797</v>
-      </c>
-      <c r="D15" s="1">
-        <v>3</v>
-      </c>
-      <c r="E15" s="7"/>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" s="1">
-        <v>302822</v>
-      </c>
-      <c r="D16" s="1">
-        <v>3</v>
-      </c>
-      <c r="E16" s="8"/>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" s="1">
-        <v>302785</v>
-      </c>
-      <c r="D17" s="1">
-        <v>4</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B18" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="1">
-        <v>302808</v>
-      </c>
-      <c r="D18" s="1">
-        <v>4</v>
-      </c>
-      <c r="E18" s="4"/>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B19" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" s="1">
-        <v>302938</v>
-      </c>
-      <c r="D19" s="1">
-        <v>4</v>
-      </c>
-      <c r="E19" s="4"/>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20" s="1">
-        <v>302776</v>
-      </c>
-      <c r="D20" s="1">
-        <v>4</v>
-      </c>
-      <c r="E20" s="5"/>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B21" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C21" s="1">
-        <v>302783</v>
-      </c>
-      <c r="D21" s="1">
-        <v>5</v>
-      </c>
-      <c r="E21" s="6"/>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="1">
-        <v>302905</v>
-      </c>
-      <c r="D22" s="1">
-        <v>5</v>
-      </c>
-      <c r="E22" s="7"/>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B23" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="1">
-        <v>303032</v>
-      </c>
-      <c r="D23" s="1">
-        <v>5</v>
-      </c>
-      <c r="E23" s="7"/>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B24" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" s="1">
-        <v>302817</v>
-      </c>
-      <c r="D24" s="1">
-        <v>5</v>
-      </c>
-      <c r="E24" s="8"/>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B25" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C25" s="1">
-        <v>302929</v>
-      </c>
-      <c r="D25" s="1">
-        <v>6</v>
-      </c>
-      <c r="E25" s="6"/>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B26" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C26" s="1">
-        <v>302787</v>
-      </c>
-      <c r="D26" s="1">
-        <v>6</v>
-      </c>
-      <c r="E26" s="7"/>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B27" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C27" s="1">
-        <v>302799</v>
-      </c>
-      <c r="D27" s="1">
-        <v>6</v>
-      </c>
-      <c r="E27" s="7"/>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B28" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" s="1">
-        <v>302798</v>
-      </c>
-      <c r="D28" s="1">
-        <v>6</v>
-      </c>
-      <c r="E28" s="8"/>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B29" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C29" s="1">
-        <v>302784</v>
-      </c>
-      <c r="D29" s="1">
-        <v>7</v>
-      </c>
-      <c r="E29" s="6"/>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B30" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C30" s="1">
-        <v>302795</v>
-      </c>
-      <c r="D30" s="1">
-        <v>7</v>
-      </c>
-      <c r="E30" s="7"/>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B31" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" s="1">
-        <v>302805</v>
-      </c>
-      <c r="D31" s="1">
-        <v>7</v>
-      </c>
-      <c r="E31" s="7"/>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B32" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C32" s="1">
-        <v>302806</v>
-      </c>
-      <c r="D32" s="1">
-        <v>7</v>
-      </c>
-      <c r="E32" s="8"/>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B33" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C33" s="1">
-        <v>302814</v>
-      </c>
-      <c r="D33" s="1">
+      <c r="F33" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B34" s="4"/>
+      <c r="C34" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D34" s="1">
+        <v>302857</v>
+      </c>
+      <c r="E34" s="1">
         <v>8</v>
       </c>
-      <c r="E33" s="9"/>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B34" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C34" s="1">
-        <v>302857</v>
-      </c>
-      <c r="D34" s="1">
+      <c r="F34" s="4"/>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B35" s="4"/>
+      <c r="C35" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D35" s="1">
+        <v>302793</v>
+      </c>
+      <c r="E35" s="1">
         <v>8</v>
       </c>
-      <c r="E34" s="10"/>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B35" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C35" s="1">
-        <v>302793</v>
-      </c>
-      <c r="D35" s="1">
+      <c r="F35" s="4"/>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B36" s="5"/>
+      <c r="C36" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D36" s="1">
+        <v>303024</v>
+      </c>
+      <c r="E36" s="1">
         <v>8</v>
       </c>
-      <c r="E35" s="10"/>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B36" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C36" s="1">
-        <v>303024</v>
-      </c>
-      <c r="D36" s="1">
-        <v>8</v>
-      </c>
-      <c r="E36" s="11"/>
+      <c r="F36" s="5"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:E37">
-    <sortCondition ref="D3:D37"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C3:F37">
+    <sortCondition ref="E3:E37"/>
   </sortState>
-  <mergeCells count="8">
-    <mergeCell ref="E25:E28"/>
-    <mergeCell ref="E29:E32"/>
-    <mergeCell ref="E33:E36"/>
-    <mergeCell ref="E3:E6"/>
-    <mergeCell ref="E7:E11"/>
-    <mergeCell ref="E12:E16"/>
-    <mergeCell ref="E17:E20"/>
-    <mergeCell ref="E21:E24"/>
+  <mergeCells count="16">
+    <mergeCell ref="B25:B28"/>
+    <mergeCell ref="B29:B32"/>
+    <mergeCell ref="B33:B36"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="B7:B11"/>
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="B21:B24"/>
+    <mergeCell ref="F25:F28"/>
+    <mergeCell ref="F29:F32"/>
+    <mergeCell ref="F33:F36"/>
+    <mergeCell ref="F3:F6"/>
+    <mergeCell ref="F7:F11"/>
+    <mergeCell ref="F12:F16"/>
+    <mergeCell ref="F17:F20"/>
+    <mergeCell ref="F21:F24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>

--- a/Project/Teams.xlsx
+++ b/Project/Teams.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch_29Oct25\all\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF82FFB1-4612-4760-89D2-02948205DC37}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{227848D0-B887-4DC6-9263-5E9DA6FD2285}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{3D2F2C73-225E-4479-9257-01007F8BBF14}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Project" sheetId="2" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!#REF!</definedName>
-  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -28,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="58">
   <si>
     <t>Kanderi Reshma Sri</t>
   </si>
@@ -132,15 +129,6 @@
     <t xml:space="preserve">Ashok Saravanan </t>
   </si>
   <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>UID</t>
-  </si>
-  <si>
-    <t>Team #</t>
-  </si>
-  <si>
     <t>Medicare Appointment System</t>
   </si>
   <si>
@@ -162,15 +150,9 @@
     <t>Mental Health Support &amp; Referral System</t>
   </si>
   <si>
-    <t>Clinic Management System</t>
-  </si>
-  <si>
     <t>Team Name</t>
   </si>
   <si>
-    <t>Project Title</t>
-  </si>
-  <si>
     <t>Care CodeX</t>
   </si>
   <si>
@@ -193,13 +175,37 @@
   </si>
   <si>
     <t>Nexus</t>
+  </si>
+  <si>
+    <t>Particpant Name</t>
+  </si>
+  <si>
+    <t>Team Leader details</t>
+  </si>
+  <si>
+    <t>Project title</t>
+  </si>
+  <si>
+    <t>Project Description</t>
+  </si>
+  <si>
+    <t>Team Project Score</t>
+  </si>
+  <si>
+    <t>Individual Project Score(Out of 100)</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>Safe Hands Connect - Clinical Management System</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -214,6 +220,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -288,7 +301,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -301,14 +314,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="45" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="45" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="45" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="45" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -623,533 +633,527 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B63DBF80-82F6-4A1E-80CA-7E30825405E4}">
-  <dimension ref="B2:F36"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="3" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A660942B-2AD3-49FF-8B8C-95DE0CDE93AA}">
+  <dimension ref="B2:I36"/>
+  <sheetFormatPr defaultColWidth="27.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B2" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" s="2" t="s">
+    <row r="2" spans="2:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B2" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
         <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="1">
-        <v>302802</v>
-      </c>
-      <c r="E3" s="1">
-        <v>1</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B4" s="4"/>
       <c r="C4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="1">
-        <v>302937</v>
-      </c>
-      <c r="E4" s="1">
-        <v>1</v>
-      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
       <c r="F4" s="4"/>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B5" s="4"/>
       <c r="C5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="1">
-        <v>302786</v>
-      </c>
-      <c r="E5" s="1">
-        <v>1</v>
-      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
       <c r="F5" s="4"/>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B6" s="5"/>
       <c r="C6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="1">
-        <v>302881</v>
-      </c>
-      <c r="E6" s="1">
-        <v>1</v>
-      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
       <c r="F6" s="5"/>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="1">
-        <v>302794</v>
-      </c>
-      <c r="E7" s="1">
+      <c r="D7" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B8" s="4"/>
       <c r="C8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="1">
-        <v>302801</v>
-      </c>
-      <c r="E8" s="1">
-        <v>2</v>
-      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
       <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4"/>
       <c r="C9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="1">
-        <v>302791</v>
-      </c>
-      <c r="E9" s="1">
-        <v>2</v>
-      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
       <c r="F9" s="4"/>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4"/>
       <c r="C10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="1">
-        <v>302796</v>
-      </c>
-      <c r="E10" s="1">
-        <v>2</v>
-      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
       <c r="F10" s="4"/>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" s="5"/>
       <c r="C11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="1">
-        <v>302970</v>
-      </c>
-      <c r="E11" s="1">
-        <v>2</v>
-      </c>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
       <c r="F11" s="5"/>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B12" s="6" t="s">
-        <v>54</v>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B12" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="1">
-        <v>302800</v>
-      </c>
-      <c r="E12" s="1">
-        <v>3</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B13" s="7"/>
+      <c r="D12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B13" s="4"/>
       <c r="C13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="1">
-        <v>302788</v>
-      </c>
-      <c r="E13" s="1">
-        <v>3</v>
-      </c>
-      <c r="F13" s="7"/>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B14" s="7"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B14" s="4"/>
       <c r="C14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="1">
-        <v>302792</v>
-      </c>
-      <c r="E14" s="1">
-        <v>3</v>
-      </c>
-      <c r="F14" s="7"/>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B15" s="7"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B15" s="4"/>
       <c r="C15" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="1">
-        <v>302797</v>
-      </c>
-      <c r="E15" s="1">
-        <v>3</v>
-      </c>
-      <c r="F15" s="7"/>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B16" s="8"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B16" s="5"/>
       <c r="C16" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="1">
-        <v>302822</v>
-      </c>
-      <c r="E16" s="1">
-        <v>3</v>
-      </c>
-      <c r="F16" s="8"/>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D17" s="1">
-        <v>302785</v>
-      </c>
-      <c r="E17" s="1">
-        <v>4</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D17" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B18" s="4"/>
       <c r="C18" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="1">
-        <v>302808</v>
-      </c>
-      <c r="E18" s="1">
-        <v>4</v>
-      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
       <c r="F18" s="4"/>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="4"/>
       <c r="C19" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="1">
-        <v>302938</v>
-      </c>
-      <c r="E19" s="1">
-        <v>4</v>
-      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
       <c r="F19" s="4"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="5"/>
       <c r="C20" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="1">
-        <v>302776</v>
-      </c>
-      <c r="E20" s="1">
-        <v>4</v>
-      </c>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
       <c r="F20" s="5"/>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D21" s="1">
-        <v>302783</v>
-      </c>
-      <c r="E21" s="1">
-        <v>5</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F21" s="3"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B22" s="4"/>
       <c r="C22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D22" s="1">
-        <v>302905</v>
-      </c>
-      <c r="E22" s="1">
-        <v>5</v>
-      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
       <c r="F22" s="4"/>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B23" s="4"/>
       <c r="C23" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="1">
-        <v>303032</v>
-      </c>
-      <c r="E23" s="1">
-        <v>5</v>
-      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
       <c r="F23" s="4"/>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B24" s="5"/>
       <c r="C24" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D24" s="1">
-        <v>302817</v>
-      </c>
-      <c r="E24" s="1">
-        <v>5</v>
-      </c>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
       <c r="F24" s="5"/>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D25" s="1">
-        <v>302929</v>
-      </c>
-      <c r="E25" s="1">
-        <v>6</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="4"/>
       <c r="C26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D26" s="1">
-        <v>302787</v>
-      </c>
-      <c r="E26" s="1">
-        <v>6</v>
-      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
       <c r="F26" s="4"/>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B27" s="4"/>
       <c r="C27" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D27" s="1">
-        <v>302799</v>
-      </c>
-      <c r="E27" s="1">
-        <v>6</v>
-      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
       <c r="F27" s="4"/>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B28" s="5"/>
       <c r="C28" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="1">
-        <v>302798</v>
-      </c>
-      <c r="E28" s="1">
-        <v>6</v>
-      </c>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
       <c r="F28" s="5"/>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B29" s="3" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D29" s="1">
-        <v>302784</v>
-      </c>
-      <c r="E29" s="1">
-        <v>7</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D29" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F29" s="3"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B30" s="4"/>
       <c r="C30" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D30" s="1">
-        <v>302795</v>
-      </c>
-      <c r="E30" s="1">
-        <v>7</v>
-      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
       <c r="F30" s="4"/>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="4"/>
       <c r="C31" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D31" s="1">
-        <v>302805</v>
-      </c>
-      <c r="E31" s="1">
-        <v>7</v>
-      </c>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
       <c r="F31" s="4"/>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="5"/>
       <c r="C32" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D32" s="1">
-        <v>302806</v>
-      </c>
-      <c r="E32" s="1">
-        <v>7</v>
-      </c>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
       <c r="F32" s="5"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B33" s="3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D33" s="1">
-        <v>302814</v>
-      </c>
-      <c r="E33" s="1">
-        <v>8</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D33" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F33" s="3"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B34" s="4"/>
       <c r="C34" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D34" s="1">
-        <v>302857</v>
-      </c>
-      <c r="E34" s="1">
-        <v>8</v>
-      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
       <c r="F34" s="4"/>
-    </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B35" s="4"/>
       <c r="C35" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D35" s="1">
-        <v>302793</v>
-      </c>
-      <c r="E35" s="1">
-        <v>8</v>
-      </c>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
       <c r="F35" s="4"/>
-    </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B36" s="5"/>
       <c r="C36" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D36" s="1">
-        <v>303024</v>
-      </c>
-      <c r="E36" s="1">
-        <v>8</v>
-      </c>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
       <c r="F36" s="5"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C3:F37">
-    <sortCondition ref="E3:E37"/>
-  </sortState>
-  <mergeCells count="16">
+  <mergeCells count="32">
+    <mergeCell ref="B29:B32"/>
+    <mergeCell ref="D29:D32"/>
+    <mergeCell ref="E29:E32"/>
+    <mergeCell ref="F29:F32"/>
+    <mergeCell ref="B33:B36"/>
+    <mergeCell ref="D33:D36"/>
+    <mergeCell ref="E33:E36"/>
+    <mergeCell ref="F33:F36"/>
+    <mergeCell ref="B21:B24"/>
+    <mergeCell ref="D21:D24"/>
+    <mergeCell ref="E21:E24"/>
+    <mergeCell ref="F21:F24"/>
     <mergeCell ref="B25:B28"/>
-    <mergeCell ref="B29:B32"/>
-    <mergeCell ref="B33:B36"/>
+    <mergeCell ref="D25:D28"/>
+    <mergeCell ref="E25:E28"/>
+    <mergeCell ref="F25:F28"/>
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="D12:D16"/>
+    <mergeCell ref="E12:E16"/>
+    <mergeCell ref="F12:F16"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="D17:D20"/>
+    <mergeCell ref="E17:E20"/>
+    <mergeCell ref="F17:F20"/>
     <mergeCell ref="B3:B6"/>
+    <mergeCell ref="D3:D6"/>
+    <mergeCell ref="E3:E6"/>
+    <mergeCell ref="F3:F6"/>
     <mergeCell ref="B7:B11"/>
-    <mergeCell ref="B12:B16"/>
-    <mergeCell ref="B17:B20"/>
-    <mergeCell ref="B21:B24"/>
-    <mergeCell ref="F25:F28"/>
-    <mergeCell ref="F29:F32"/>
-    <mergeCell ref="F33:F36"/>
-    <mergeCell ref="F3:F6"/>
+    <mergeCell ref="D7:D11"/>
+    <mergeCell ref="E7:E11"/>
     <mergeCell ref="F7:F11"/>
-    <mergeCell ref="F12:F16"/>
-    <mergeCell ref="F17:F20"/>
-    <mergeCell ref="F21:F24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
 </file>
--- a/Project/Teams.xlsx
+++ b/Project/Teams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch_29Oct25\all\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{227848D0-B887-4DC6-9263-5E9DA6FD2285}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C50B086-2E64-4946-8F90-E2616DD7B679}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{3D2F2C73-225E-4479-9257-01007F8BBF14}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="57">
   <si>
     <t>Kanderi Reshma Sri</t>
   </si>
@@ -40,9 +40,6 @@
   </si>
   <si>
     <t>Sanjay Kumar Sadasivam</t>
-  </si>
-  <si>
-    <t>Mallamgunta Geetha sri</t>
   </si>
   <si>
     <t>Niranj K V</t>
@@ -305,6 +302,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="45" wrapText="1"/>
     </xf>
@@ -313,12 +316,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="45" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -634,525 +631,513 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A660942B-2AD3-49FF-8B8C-95DE0CDE93AA}">
-  <dimension ref="B2:I36"/>
+  <dimension ref="B2:I35"/>
   <sheetFormatPr defaultColWidth="27.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="2:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B2" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C2" s="7" t="s">
+      <c r="B2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="E2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="G2" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="H2" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="I2" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>56</v>
-      </c>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
-        <v>46</v>
+      <c r="B3" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" s="3"/>
+      <c r="D3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" s="5"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="4"/>
+      <c r="B4" s="6"/>
       <c r="C4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
+        <v>7</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="4"/>
+      <c r="B5" s="6"/>
       <c r="C5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
+        <v>20</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="5"/>
+      <c r="B6" s="7"/>
       <c r="C6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
+        <v>22</v>
+      </c>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="3" t="s">
-        <v>43</v>
+      <c r="B7" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" s="3"/>
+      <c r="E7" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="5"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B8" s="4"/>
+      <c r="B8" s="6"/>
       <c r="C8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="4"/>
+      <c r="B9" s="6"/>
       <c r="C9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
+        <v>13</v>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B10" s="4"/>
+      <c r="B10" s="7"/>
       <c r="C10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
+        <v>21</v>
+      </c>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B11" s="5"/>
+      <c r="B11" s="5" t="s">
+        <v>48</v>
+      </c>
       <c r="C11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
+        <v>8</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>37</v>
+      </c>
       <c r="F11" s="5"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B12" s="3" t="s">
-        <v>49</v>
-      </c>
+      <c r="B12" s="6"/>
       <c r="C12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B13" s="4"/>
+      <c r="B13" s="6"/>
       <c r="C13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
+        <v>25</v>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B14" s="4"/>
+      <c r="B14" s="6"/>
       <c r="C14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
+        <v>27</v>
+      </c>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B15" s="4"/>
+      <c r="B15" s="7"/>
       <c r="C15" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
+        <v>29</v>
+      </c>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B16" s="5"/>
+      <c r="B16" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C16" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
+        <v>12</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>34</v>
+      </c>
       <c r="F16" s="5"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B17" s="3" t="s">
-        <v>47</v>
-      </c>
+      <c r="B17" s="6"/>
       <c r="C17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F17" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B18" s="4"/>
+      <c r="B18" s="6"/>
       <c r="C18" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
+        <v>26</v>
+      </c>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B19" s="4"/>
+      <c r="B19" s="7"/>
       <c r="C19" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
+        <v>28</v>
+      </c>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B20" s="5"/>
+      <c r="B20" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="C20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>35</v>
+      </c>
       <c r="F20" s="5"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B21" s="3" t="s">
-        <v>48</v>
-      </c>
+      <c r="B21" s="6"/>
       <c r="C21" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F21" s="3"/>
+        <v>6</v>
+      </c>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B22" s="4"/>
+      <c r="B22" s="6"/>
       <c r="C22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
+        <v>9</v>
+      </c>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B23" s="4"/>
+      <c r="B23" s="7"/>
       <c r="C23" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
+        <v>16</v>
+      </c>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B24" s="5"/>
+      <c r="B24" s="5" t="s">
+        <v>41</v>
+      </c>
       <c r="C24" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
+        <v>1</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>38</v>
+      </c>
       <c r="F24" s="5"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B25" s="3" t="s">
-        <v>42</v>
-      </c>
+      <c r="B25" s="6"/>
       <c r="C25" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F25" s="3"/>
+        <v>24</v>
+      </c>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B26" s="4"/>
+      <c r="B26" s="6"/>
       <c r="C26" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
+        <v>11</v>
+      </c>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B27" s="4"/>
+      <c r="B27" s="7"/>
       <c r="C27" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B28" s="5"/>
+      <c r="B28" s="5" t="s">
+        <v>43</v>
+      </c>
       <c r="C28" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
+        <v>0</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>56</v>
+      </c>
       <c r="F28" s="5"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B29" s="3" t="s">
-        <v>44</v>
-      </c>
+      <c r="B29" s="6"/>
       <c r="C29" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F29" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B30" s="4"/>
+      <c r="B30" s="6"/>
       <c r="C30" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
+        <v>15</v>
+      </c>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B31" s="4"/>
+      <c r="B31" s="7"/>
       <c r="C31" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B32" s="5"/>
+      <c r="B32" s="5" t="s">
+        <v>44</v>
+      </c>
       <c r="C32" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
+        <v>23</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>39</v>
+      </c>
       <c r="F32" s="5"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B33" s="3" t="s">
-        <v>45</v>
-      </c>
+      <c r="B33" s="6"/>
       <c r="C33" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F33" s="3"/>
+        <v>32</v>
+      </c>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B34" s="4"/>
+      <c r="B34" s="6"/>
       <c r="C34" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
+        <v>30</v>
+      </c>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B35" s="4"/>
+      <c r="B35" s="7"/>
       <c r="C35" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
     </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B36" s="5"/>
-      <c r="C36" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-    </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="B29:B32"/>
-    <mergeCell ref="D29:D32"/>
-    <mergeCell ref="E29:E32"/>
-    <mergeCell ref="F29:F32"/>
-    <mergeCell ref="B33:B36"/>
-    <mergeCell ref="D33:D36"/>
-    <mergeCell ref="E33:E36"/>
-    <mergeCell ref="F33:F36"/>
-    <mergeCell ref="B21:B24"/>
-    <mergeCell ref="D21:D24"/>
-    <mergeCell ref="E21:E24"/>
-    <mergeCell ref="F21:F24"/>
-    <mergeCell ref="B25:B28"/>
-    <mergeCell ref="D25:D28"/>
-    <mergeCell ref="E25:E28"/>
-    <mergeCell ref="F25:F28"/>
-    <mergeCell ref="B12:B16"/>
-    <mergeCell ref="D12:D16"/>
-    <mergeCell ref="E12:E16"/>
-    <mergeCell ref="F12:F16"/>
-    <mergeCell ref="B17:B20"/>
-    <mergeCell ref="D17:D20"/>
-    <mergeCell ref="E17:E20"/>
-    <mergeCell ref="F17:F20"/>
     <mergeCell ref="B3:B6"/>
     <mergeCell ref="D3:D6"/>
     <mergeCell ref="E3:E6"/>
     <mergeCell ref="F3:F6"/>
-    <mergeCell ref="B7:B11"/>
-    <mergeCell ref="D7:D11"/>
-    <mergeCell ref="E7:E11"/>
-    <mergeCell ref="F7:F11"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="D7:D10"/>
+    <mergeCell ref="E7:E10"/>
+    <mergeCell ref="F7:F10"/>
+    <mergeCell ref="B11:B15"/>
+    <mergeCell ref="D11:D15"/>
+    <mergeCell ref="E11:E15"/>
+    <mergeCell ref="F11:F15"/>
+    <mergeCell ref="B16:B19"/>
+    <mergeCell ref="D16:D19"/>
+    <mergeCell ref="E16:E19"/>
+    <mergeCell ref="F16:F19"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="D20:D23"/>
+    <mergeCell ref="E20:E23"/>
+    <mergeCell ref="F20:F23"/>
+    <mergeCell ref="B24:B27"/>
+    <mergeCell ref="D24:D27"/>
+    <mergeCell ref="E24:E27"/>
+    <mergeCell ref="F24:F27"/>
+    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="D28:D31"/>
+    <mergeCell ref="E28:E31"/>
+    <mergeCell ref="F28:F31"/>
+    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="D32:D35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="F32:F35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
